--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104756_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104756_W34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1816</v>
+        <v>3.6207</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7562</v>
+        <v>0.9443</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4254</v>
+        <v>2.6763</v>
       </c>
       <c r="G2" t="n">
         <v>0.2228</v>
@@ -610,13 +610,13 @@
         <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9101</v>
+        <v>1.3492</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8496</v>
+        <v>1.0377</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0605</v>
+        <v>0.3115</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.846</v>
+        <v>3.3959</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7592</v>
+        <v>3.5321</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0868</v>
+        <v>-0.1362</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0514</v>
+        <v>2.0439</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0321</v>
+        <v>-0.8618</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0193</v>
+        <v>2.9058</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7335</v>
+        <v>3.1026</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4137</v>
+        <v>0.0722</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3198</v>
+        <v>3.0304</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7849</v>
+        <v>-1.0587</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4458</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3391</v>
+        <v>-0.1246</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5934</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5934</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>1.691</v>
+        <v>0.4901</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.4782</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9808</v>
+        <v>0.0119</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.387</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3155</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>D. NEEDHAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3159</v>
+        <v>3.3857</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5148</v>
+        <v>5.5316</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1989</v>
+        <v>-2.1459</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0439</v>
+        <v>3.6183</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8618</v>
+        <v>-2.0251</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9058</v>
+        <v>5.6434</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1026</v>
+        <v>4.9491</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0722</v>
+        <v>-0.7174</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0304</v>
+        <v>5.6666</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0587</v>
+        <v>-1.3309</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-1.3077</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1246</v>
+        <v>-0.0232</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2276</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5899</v>
+        <v>-0.0536</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5391</v>
+        <v>0.5825</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0508</v>
+        <v>-0.6361</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0895</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0895</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0526</v>
+        <v>2.3722</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4254</v>
+        <v>1.6617</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3728</v>
+        <v>0.7104</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4622</v>
+        <v>-0.0514</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5886</v>
+        <v>-0.0321</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0508</v>
+        <v>-0.0193</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6628</v>
+        <v>0.7335</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9415</v>
+        <v>0.4137</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6043</v>
+        <v>0.3198</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2006</v>
+        <v>-0.7849</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6471</v>
+        <v>-0.4458</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5535</v>
+        <v>-0.3391</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2276</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9105</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1336</v>
+        <v>1.2171</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9008</v>
+        <v>0.6127</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2328</v>
+        <v>0.6044</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3155</v>
+        <v>-0.387</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3155</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>C. HILDRETH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9462</v>
+        <v>2.1177</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3663</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4201</v>
+        <v>2.1256</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.3962</v>
+        <v>-0.3977</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.5322</v>
+        <v>-1.9231</v>
       </c>
       <c r="I6" t="n">
-        <v>0.136</v>
+        <v>1.5254</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.081</v>
+        <v>-1.0586</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.0864</v>
+        <v>-1.5351</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0054</v>
+        <v>0.4764</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3152</v>
+        <v>0.6609</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4458</v>
+        <v>-0.3881</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8694</v>
+        <v>1.049</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9105</v>
+        <v>1.5934</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9105</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>3.5001</v>
+        <v>0.922</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>0.506</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3001</v>
+        <v>0.416</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9317</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2472</v>
+        <v>0.5447</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3155</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. HILDRETH</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8181</v>
+        <v>1.5788</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2448</v>
+        <v>2.1398</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0629</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3977</v>
+        <v>1.4622</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9231</v>
+        <v>-1.5886</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5254</v>
+        <v>3.0508</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0586</v>
+        <v>2.6628</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.5351</v>
+        <v>-0.9415</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4764</v>
+        <v>3.6043</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6609</v>
+        <v>-1.2006</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3881</v>
+        <v>-0.6471</v>
       </c>
       <c r="O7" t="n">
-        <v>1.049</v>
+        <v>-0.5535</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5934</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5934</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6224</v>
+        <v>0.6597</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2691</v>
+        <v>0.6151</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3533</v>
+        <v>0.0446</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5447</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5447</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. NEEDHAM</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3998</v>
+        <v>1.0633</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9221</v>
+        <v>-0.5201</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5223</v>
+        <v>1.5834</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6183</v>
+        <v>-1.4889</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0251</v>
+        <v>-1.0883</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6434</v>
+        <v>-0.4006</v>
       </c>
       <c r="J8" t="n">
-        <v>4.9491</v>
+        <v>-1.5762</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7174</v>
+        <v>-0.1831</v>
       </c>
       <c r="L8" t="n">
-        <v>5.6666</v>
+        <v>-1.3931</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3309</v>
+        <v>0.0873</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3077</v>
+        <v>-0.9052</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0232</v>
+        <v>0.9925</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9105</v>
+        <v>2.0487</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9105</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.0395</v>
+        <v>1.4352</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.027</v>
+        <v>0.8983</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0125</v>
+        <v>0.5369</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0895</v>
+        <v>-0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
         <v>-1.0895</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0634</v>
+        <v>0.0196</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7082000000000001</v>
+        <v>0.6593</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7716</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4889</v>
+        <v>-3.3962</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0883</v>
+        <v>-3.5322</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4006</v>
+        <v>0.136</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5762</v>
+        <v>-2.081</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1831</v>
+        <v>-3.0864</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3931</v>
+        <v>1.0054</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0873</v>
+        <v>-1.3152</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9052</v>
+        <v>-0.4458</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9925</v>
+        <v>-0.8694</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0487</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0487</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4353</v>
+        <v>1.5736</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7102000000000001</v>
+        <v>1.493</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7251</v>
+        <v>0.0805</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9317</v>
+        <v>0.9317</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1578</v>
+        <v>1.2472</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0895</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. KARNIK</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3353</v>
+        <v>-3.4285</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6211</v>
+        <v>-1.7783</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2857</v>
+        <v>-1.6502</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.4347</v>
+        <v>-1.423</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.712</v>
+        <v>-1.2574</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2773</v>
+        <v>-0.1656</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.3496</v>
+        <v>0.15</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.6344</v>
+        <v>-0.4524</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7151999999999999</v>
+        <v>0.6024</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0851</v>
+        <v>-1.5729</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0775</v>
+        <v>-0.805</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9925</v>
+        <v>-0.768</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1382</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1382</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9415</v>
+        <v>-0.0267</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7089</v>
+        <v>0.348</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2326</v>
+        <v>-0.3747</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1578</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1578</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>J. KARNIK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0174</v>
+        <v>-4.1575</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0849</v>
+        <v>-5.3805</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9325</v>
+        <v>1.223</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.423</v>
+        <v>-5.4347</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2574</v>
+        <v>-5.712</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1656</v>
+        <v>0.2773</v>
       </c>
       <c r="J11" t="n">
-        <v>0.15</v>
+        <v>-5.3496</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4524</v>
+        <v>-4.6344</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6024</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5729</v>
+        <v>-0.0851</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.805</v>
+        <v>-1.0775</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.768</v>
+        <v>0.9925</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8211</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2763</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4553</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6156</v>
+        <v>1.1194</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0414</v>
+        <v>0.9495</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.657</v>
+        <v>0.1699</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1578</v>
+        <v>0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.270899999999999</v>
+        <v>9.9679</v>
       </c>
       <c r="E12" t="n">
-        <v>6.085</v>
+        <v>6.782</v>
       </c>
       <c r="F12" t="n">
         <v>3.1858</v>
@@ -1363,7 +1363,7 @@
         <v>16.1915</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4392</v>
+        <v>1.439200000000001</v>
       </c>
       <c r="K12" t="n">
         <v>-13.3471</v>
@@ -1390,16 +1390,16 @@
         <v>12.5197</v>
       </c>
       <c r="S12" t="n">
-        <v>7.989000000000002</v>
+        <v>8.686</v>
       </c>
       <c r="T12" t="n">
-        <v>6.8241</v>
+        <v>7.521000000000001</v>
       </c>
       <c r="U12" t="n">
         <v>1.1649</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7024999999999999</v>
+        <v>-0.7025000000000001</v>
       </c>
       <c r="W12" t="n">
         <v>3.5125</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6872</v>
+        <v>2.901</v>
       </c>
       <c r="E13" t="n">
-        <v>4.393</v>
+        <v>1.2589</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7059</v>
+        <v>1.6421</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7168</v>
+        <v>3.154</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4651</v>
+        <v>3.8974</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2517</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4741</v>
+        <v>1.6425</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9201</v>
+        <v>2.2613</v>
       </c>
       <c r="L13" t="n">
-        <v>2.554</v>
+        <v>-0.6188</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7573</v>
+        <v>1.5115</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5451</v>
+        <v>1.6361</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.3023</v>
+        <v>-0.1246</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4553</v>
+        <v>0.6829</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.2276</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6829</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1996</v>
+        <v>-0.9359</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8310999999999999</v>
+        <v>-0.156</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6315</v>
+        <v>-0.7799</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9929</v>
+        <v>2.4016</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6666</v>
+        <v>3.9193</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3263</v>
+        <v>-1.5177</v>
       </c>
       <c r="G14" t="n">
-        <v>3.154</v>
+        <v>1.7168</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8974</v>
+        <v>1.4651</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7433999999999999</v>
+        <v>0.2517</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6425</v>
+        <v>3.4741</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2613</v>
+        <v>0.9201</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6188</v>
+        <v>2.554</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5115</v>
+        <v>-1.7573</v>
       </c>
       <c r="N14" t="n">
-        <v>1.6361</v>
+        <v>0.5451</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1246</v>
+        <v>-2.3023</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6829</v>
+        <v>0.4553</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9105</v>
+        <v>0.6829</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.844</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7482</v>
+        <v>0.3573</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0957</v>
+        <v>-0.4433</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1464</v>
+        <v>1.2484</v>
       </c>
       <c r="E15" t="n">
-        <v>1.051</v>
+        <v>1.8801</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1973</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>4.608</v>
@@ -1624,13 +1624,13 @@
         <v>0.2276</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.3203</v>
+        <v>-0.9255</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.0585</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4327</v>
+        <v>-0.867</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1578</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1696</v>
+        <v>-0.2544</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4181</v>
+        <v>-0.7146</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5878</v>
+        <v>0.4602</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7038</v>
+        <v>-1.6355</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9352</v>
+        <v>-0.006</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2314</v>
+        <v>-1.6294</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2529</v>
+        <v>-1.4531</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1411</v>
+        <v>-0.7379</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4509</v>
+        <v>-0.1824</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7941</v>
+        <v>0.7319</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3432</v>
+        <v>-0.9143</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2276</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2276</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4437</v>
+        <v>-0.1637</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6904</v>
+        <v>-0.351</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2467</v>
+        <v>0.1873</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0895</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7025</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>D. NIEBLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1858</v>
+        <v>-0.5688</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.833</v>
+        <v>-0.8955</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6473</v>
+        <v>0.3267</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6355</v>
+        <v>-0.5468</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.006</v>
+        <v>0.7924</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6294</v>
+        <v>-1.3392</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.4531</v>
+        <v>-0.7352</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7379</v>
+        <v>0.0172</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.7524</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1824</v>
+        <v>0.1884</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7319</v>
+        <v>0.7752</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9143</v>
+        <v>-0.5868</v>
       </c>
       <c r="P17" t="n">
         <v>0.4553</v>
@@ -1780,19 +1780,19 @@
         <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.095</v>
+        <v>-0.4773</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4694</v>
+        <v>-0.1604</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3744</v>
+        <v>-0.317</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0895</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0895</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. NIEBLA</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9393</v>
+        <v>-0.856</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.014</v>
+        <v>1.3521</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0747</v>
+        <v>-2.2081</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5468</v>
+        <v>0.7038</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7924</v>
+        <v>1.9352</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3392</v>
+        <v>-1.2314</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7352</v>
+        <v>0.2529</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0172</v>
+        <v>0.1411</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7524</v>
+        <v>0.1117</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1884</v>
+        <v>0.4509</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7752</v>
+        <v>1.7941</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5868</v>
+        <v>-1.3432</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4553</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4553</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8478</v>
+        <v>-0.2426</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2788</v>
+        <v>0.6244</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.569</v>
+        <v>-0.867</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.999</v>
+        <v>-1.0142</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4584</v>
+        <v>0.2215</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4575</v>
+        <v>-1.2357</v>
       </c>
       <c r="G19" t="n">
         <v>0.4152</v>
@@ -1936,13 +1936,13 @@
         <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8012</v>
+        <v>-0.8163</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1165</v>
+        <v>-0.3534</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6847</v>
+        <v>-0.4629</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1578</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7917</v>
+        <v>-1.8544</v>
       </c>
       <c r="E20" t="n">
         <v>-3.4616</v>
       </c>
       <c r="F20" t="n">
-        <v>1.67</v>
+        <v>1.6073</v>
       </c>
       <c r="G20" t="n">
         <v>1.2649</v>
@@ -2014,13 +2014,13 @@
         <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0974</v>
+        <v>-0.1601</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1906</v>
       </c>
       <c r="U20" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0305</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.705</v>
+        <v>-2.4324</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5521</v>
+        <v>-1.8414</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1529</v>
+        <v>-0.591</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4015</v>
@@ -2092,13 +2092,13 @@
         <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6011</v>
+        <v>-0.3284</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8179</v>
+        <v>-0.1072</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2169</v>
+        <v>-0.2212</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1578</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2912</v>
+        <v>-2.7628</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.133</v>
+        <v>-2.0145</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1583</v>
+        <v>-0.7483</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4855</v>
@@ -2170,13 +2170,13 @@
         <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3913</v>
+        <v>-0.8629</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6785</v>
+        <v>-0.5601</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7128</v>
+        <v>-0.3028</v>
       </c>
       <c r="V22" t="n">
         <v>1.0895</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7229</v>
+        <v>-3.71</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1794</v>
+        <v>-2.8901</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5435</v>
+        <v>-0.8199</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9489</v>
@@ -2248,13 +2248,13 @@
         <v>0.2276</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6343</v>
+        <v>-0.6214</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5011</v>
+        <v>-0.2096</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1354</v>
+        <v>-0.4118</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2292</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.270800000000001</v>
+        <v>-6.902</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.185999999999998</v>
+        <v>-3.1858</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.084899999999999</v>
+        <v>-3.716</v>
       </c>
       <c r="G24" t="n">
-        <v>4.8445</v>
+        <v>4.844499999999998</v>
       </c>
       <c r="H24" t="n">
         <v>21.036</v>
@@ -2302,7 +2302,7 @@
         <v>6.283700000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>7.689</v>
+        <v>7.689000000000002</v>
       </c>
       <c r="L24" t="n">
         <v>-1.4051</v>
@@ -2326,19 +2326,19 @@
         <v>5.690799999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.9891</v>
+        <v>-5.620099999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1649</v>
+        <v>-1.1651</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.824</v>
+        <v>-4.455100000000001</v>
       </c>
       <c r="V24" t="n">
         <v>0.7024</v>
       </c>
       <c r="W24" t="n">
-        <v>4.215100000000001</v>
+        <v>4.2151</v>
       </c>
       <c r="X24" t="n">
         <v>-3.5125</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104756_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104756_W34.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-4.215</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104756_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-3.5125</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
